--- a/dist/成果/沟道纵断面成果表_AFAE900122HF0000ZACS017.xlsx
+++ b/dist/成果/沟道纵断面成果表_AFAE900122HF0000ZACS017.xlsx
@@ -794,7 +794,7 @@
         <v>45.214</v>
       </c>
       <c r="F11" s="22" t="n">
-        <v>45.31512334055012</v>
+        <v>45.6144605132709</v>
       </c>
       <c r="G11" s="23" t="n">
         <v>115.650663</v>
@@ -822,7 +822,7 @@
         <v>44.705</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>45.0070038944086</v>
+        <v>45.06249706634811</v>
       </c>
       <c r="G12" s="23" t="n">
         <v>115.650244</v>
@@ -850,7 +850,7 @@
         <v>44.384</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>44.76468537552548</v>
+        <v>44.65007524823293</v>
       </c>
       <c r="G13" s="23" t="n">
         <v>115.64949</v>
@@ -878,7 +878,7 @@
         <v>44.098</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>44.49406137297103</v>
+        <v>44.2339329954287</v>
       </c>
       <c r="G14" s="23" t="n">
         <v>115.648828</v>
@@ -906,7 +906,7 @@
         <v>43.801</v>
       </c>
       <c r="F15" s="22" t="n">
-        <v>43.92015762507986</v>
+        <v>44.07328199806714</v>
       </c>
       <c r="G15" s="23" t="n">
         <v>115.648473</v>
@@ -934,7 +934,7 @@
         <v>43.564</v>
       </c>
       <c r="F16" s="22" t="n">
-        <v>43.66618514208319</v>
+        <v>43.86567470410626</v>
       </c>
       <c r="G16" s="23" t="n">
         <v>115.648433</v>
@@ -962,7 +962,7 @@
         <v>43.035</v>
       </c>
       <c r="F17" s="22" t="n">
-        <v>43.26174343915595</v>
+        <v>43.25462699899818</v>
       </c>
       <c r="G17" s="23" t="n">
         <v>115.648426</v>
@@ -990,7 +990,7 @@
         <v>43.102</v>
       </c>
       <c r="F18" s="22" t="n">
-        <v>43.59230378441967</v>
+        <v>43.47380829123758</v>
       </c>
       <c r="G18" s="23" t="n">
         <v>115.648421</v>
@@ -1018,7 +1018,7 @@
         <v>42.586</v>
       </c>
       <c r="F19" s="22" t="n">
-        <v>42.66391302896682</v>
+        <v>42.87884556149558</v>
       </c>
       <c r="G19" s="23" t="n">
         <v>115.648412</v>
@@ -1046,7 +1046,7 @@
         <v>42.314</v>
       </c>
       <c r="F20" s="22" t="n">
-        <v>42.31838563277412</v>
+        <v>42.59899598828019</v>
       </c>
       <c r="G20" s="23" t="n">
         <v>115.64834</v>
@@ -1074,7 +1074,7 @@
         <v>42.783</v>
       </c>
       <c r="F21" s="22" t="n">
-        <v>42.88459578694198</v>
+        <v>42.92646704371067</v>
       </c>
       <c r="G21" s="23" t="n">
         <v>115.648338</v>
@@ -1102,7 +1102,7 @@
         <v>42.875</v>
       </c>
       <c r="F22" s="22" t="n">
-        <v>43.36912570711274</v>
+        <v>43.00852474756655</v>
       </c>
       <c r="G22" s="23" t="n">
         <v>115.648336</v>
@@ -1130,7 +1130,7 @@
         <v>41.367</v>
       </c>
       <c r="F23" s="22" t="n">
-        <v>41.82631025622769</v>
+        <v>41.43601676607672</v>
       </c>
       <c r="G23" s="23" t="n">
         <v>115.648228</v>
@@ -1158,7 +1158,7 @@
         <v>40.356</v>
       </c>
       <c r="F24" s="22" t="n">
-        <v>40.70242840722257</v>
+        <v>40.42204621897536</v>
       </c>
       <c r="G24" s="23" t="n">
         <v>115.647461</v>
@@ -1186,7 +1186,7 @@
         <v>39.515</v>
       </c>
       <c r="F25" s="22" t="n">
-        <v>39.66424966745608</v>
+        <v>39.54653624757869</v>
       </c>
       <c r="G25" s="23" t="n">
         <v>115.646541</v>
@@ -1214,7 +1214,7 @@
         <v>39.761</v>
       </c>
       <c r="F26" s="22" t="n">
-        <v>40.19680435649901</v>
+        <v>40.21697170783204</v>
       </c>
       <c r="G26" s="23" t="n">
         <v>115.646434</v>
@@ -1242,7 +1242,7 @@
         <v>40.178</v>
       </c>
       <c r="F27" s="22" t="n">
-        <v>40.21338920826944</v>
+        <v>40.30679702713689</v>
       </c>
       <c r="G27" s="23" t="n">
         <v>115.646425</v>
@@ -1270,7 +1270,7 @@
         <v>40.094</v>
       </c>
       <c r="F28" s="22" t="n">
-        <v>40.14633573702652</v>
+        <v>40.25956493659355</v>
       </c>
       <c r="G28" s="23" t="n">
         <v>115.646401</v>
@@ -1298,7 +1298,7 @@
         <v>39.146</v>
       </c>
       <c r="F29" s="22" t="n">
-        <v>39.63292205149274</v>
+        <v>39.56708255330831</v>
       </c>
       <c r="G29" s="23" t="n">
         <v>115.646387</v>
@@ -1326,7 +1326,7 @@
         <v>39.184</v>
       </c>
       <c r="F30" s="22" t="n">
-        <v>39.23900663055029</v>
+        <v>39.25239665438547</v>
       </c>
       <c r="G30" s="23" t="n">
         <v>115.646349</v>
@@ -1354,7 +1354,7 @@
         <v>39.436</v>
       </c>
       <c r="F31" s="22" t="n">
-        <v>39.47980255113048</v>
+        <v>39.53594859582554</v>
       </c>
       <c r="G31" s="23" t="n">
         <v>115.646347</v>
@@ -1382,7 +1382,7 @@
         <v>39.12</v>
       </c>
       <c r="F32" s="22" t="n">
-        <v>39.25278779519051</v>
+        <v>39.35983386624099</v>
       </c>
       <c r="G32" s="23" t="n">
         <v>115.645949</v>
@@ -1410,7 +1410,7 @@
         <v>38.769</v>
       </c>
       <c r="F33" s="22" t="n">
-        <v>39.00992045079853</v>
+        <v>38.89534858470279</v>
       </c>
       <c r="G33" s="23" t="n">
         <v>115.645625</v>
@@ -1438,7 +1438,7 @@
         <v>38</v>
       </c>
       <c r="F34" s="22" t="n">
-        <v>38.45980820699854</v>
+        <v>38.26919819446429</v>
       </c>
       <c r="G34" s="23" t="n">
         <v>115.645125</v>
@@ -1466,7 +1466,7 @@
         <v>37.552</v>
       </c>
       <c r="F35" s="22" t="n">
-        <v>37.69569896277563</v>
+        <v>37.6185554361333</v>
       </c>
       <c r="G35" s="23" t="n">
         <v>115.645112</v>
@@ -1494,7 +1494,7 @@
         <v>37.455</v>
       </c>
       <c r="F36" s="22" t="n">
-        <v>37.57804330522962</v>
+        <v>37.62200935438966</v>
       </c>
       <c r="G36" s="23" t="n">
         <v>115.645038</v>
@@ -1522,7 +1522,7 @@
         <v>37.033</v>
       </c>
       <c r="F37" s="22" t="n">
-        <v>37.03536998478194</v>
+        <v>37.28372731200532</v>
       </c>
       <c r="G37" s="23" t="n">
         <v>115.644503</v>
@@ -1550,7 +1550,7 @@
         <v>36.5</v>
       </c>
       <c r="F38" s="22" t="n">
-        <v>36.572578430562</v>
+        <v>36.6175754590496</v>
       </c>
       <c r="G38" s="23" t="n">
         <v>115.644049</v>
@@ -1578,7 +1578,7 @@
         <v>36.473</v>
       </c>
       <c r="F39" s="22" t="n">
-        <v>36.9336469971918</v>
+        <v>36.9461149883672</v>
       </c>
       <c r="G39" s="23" t="n">
         <v>115.64372</v>
@@ -1606,7 +1606,7 @@
         <v>36.402</v>
       </c>
       <c r="F40" s="22" t="n">
-        <v>36.89447443156543</v>
+        <v>36.4351841864403</v>
       </c>
       <c r="G40" s="23" t="n">
         <v>115.643623</v>
@@ -1634,7 +1634,7 @@
         <v>36.218</v>
       </c>
       <c r="F41" s="22" t="n">
-        <v>36.23519721372311</v>
+        <v>36.26048138171915</v>
       </c>
       <c r="G41" s="23" t="n">
         <v>115.643429</v>
@@ -1662,7 +1662,7 @@
         <v>35.858</v>
       </c>
       <c r="F42" s="22" t="n">
-        <v>35.96017869014648</v>
+        <v>36.02396708722457</v>
       </c>
       <c r="G42" s="23" t="n">
         <v>115.643254</v>
@@ -1690,7 +1690,7 @@
         <v>35.521</v>
       </c>
       <c r="F43" s="22" t="n">
-        <v>35.54974136029791</v>
+        <v>35.66441023602279</v>
       </c>
       <c r="G43" s="23" t="n">
         <v>115.642583</v>
@@ -1718,7 +1718,7 @@
         <v>33.868</v>
       </c>
       <c r="F44" s="22" t="n">
-        <v>34.23320579696909</v>
+        <v>33.93881579934955</v>
       </c>
       <c r="G44" s="23" t="n">
         <v>115.641487</v>
@@ -1746,7 +1746,7 @@
         <v>32.794</v>
       </c>
       <c r="F45" s="22" t="n">
-        <v>32.94088174526841</v>
+        <v>33.20570221864159</v>
       </c>
       <c r="G45" s="23" t="n">
         <v>115.640803</v>
@@ -1770,16 +1770,16 @@
     <mergeCell ref="D3:H3"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="D2:H2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="D2:H2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation sqref="B7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"85高程系,假定高程系"</formula1>
     </dataValidation>
-    <dataValidation sqref="D7:H7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="D7:H7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"水准仪／卷尺测量法,GNSS RTK测量法,全站仪法,三维激光扫描方法"</formula1>
     </dataValidation>
   </dataValidations>
